--- a/outputs/daily/hr_rankings_2026-10-08.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-08.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.9</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1312,12 +1320,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.3</v>
+        <v>48.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1636,7 +1648,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S5" t="n">
         <v>90.40000000000001</v>
@@ -1824,8 +1836,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1864,12 +1884,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,7 +1908,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>42.9</v>
+        <v>41.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1922,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1932,10 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -1925,39 +1945,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2100,8 +2116,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2140,7 +2164,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2188,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>39.9</v>
+        <v>40.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2202,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2212,10 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -2201,39 +2225,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2396,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2416,7 +2444,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2468,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.3</v>
+        <v>38.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2464,7 +2492,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S8" t="n">
         <v>92.09999999999999</v>
@@ -2652,8 +2680,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2667,12 +2703,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,12 +2728,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2716,7 +2752,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>36.6</v>
+        <v>37.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,62 +2766,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>44.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2805,27 +2837,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,67 +2867,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2928,8 +2960,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2943,24 +2983,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -2968,22 +3008,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2992,7 +3032,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>36.2</v>
+        <v>37.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,65 +3046,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>44.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3081,27 +3117,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,101 +3147,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -3219,12 +3263,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3244,12 +3288,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3268,7 +3312,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>36.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,62 +3326,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>49.9</v>
       </c>
       <c r="Q11" t="n">
         <v>21.5</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>77.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3357,27 +3397,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,67 +3427,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3480,8 +3520,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -3495,12 +3543,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3520,12 +3568,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3592,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>36.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,26 +3606,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.3</v>
+        <v>25.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>10.1</v>
+        <v>23.4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3591,7 +3639,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3633,12 +3681,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,12 +3696,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3663,67 +3711,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3756,8 +3804,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -3771,12 +3827,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3852,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3876,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,26 +3890,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>10.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3867,7 +3923,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3909,27 +3965,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,67 +3995,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4088,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4047,24 +4111,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4072,22 +4136,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4096,7 +4160,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>33.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,65 +4174,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>45</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4185,7 +4245,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -4195,17 +4255,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,101 +4275,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4323,24 +4391,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4348,7 +4416,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4358,12 +4426,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4372,7 +4440,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.6</v>
+        <v>33.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4390,13 +4458,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S15" t="n">
         <v>47.9</v>
@@ -4405,7 +4473,7 @@
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4444,7 +4512,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4461,27 +4529,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,101 +4559,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4599,24 +4675,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4624,22 +4700,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4724,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>27.7</v>
+        <v>32.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4666,22 +4742,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>22.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>36.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4695,7 +4771,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4720,7 +4796,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,12 +4813,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4828,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4843,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.2967</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4900,7 +4984,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +5008,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4948,7 +5032,7 @@
         <v>9.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S17" t="n">
         <v>40.2</v>
@@ -5136,8 +5220,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -5176,7 +5268,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5292,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5224,7 +5316,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -5412,8 +5504,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -5452,7 +5552,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5576,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5500,7 +5600,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S19" t="n">
         <v>88.7</v>
@@ -5688,8 +5788,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6054,7 +6162,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,7 +6186,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6200,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6210,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6223,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6290,8 +6394,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6330,12 +6442,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,7 +6466,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.9</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6480,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6490,10 @@
         <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -6391,39 +6503,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6674,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6606,12 +6722,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6630,7 +6746,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.3</v>
+        <v>48.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6760,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6770,10 @@
         <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -6667,39 +6783,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6954,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6882,7 +7002,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +7026,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6930,7 +7050,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S5" t="n">
         <v>90.40000000000001</v>
@@ -7118,8 +7238,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7158,12 +7286,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7182,7 +7310,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>42.9</v>
+        <v>41.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7324,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7334,10 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -7219,39 +7347,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7394,8 +7518,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7434,7 +7566,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7590,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>39.9</v>
+        <v>40.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7604,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7614,10 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -7495,39 +7627,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7798,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7710,7 +7846,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7870,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.3</v>
+        <v>38.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7758,7 +7894,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S8" t="n">
         <v>92.09999999999999</v>
@@ -7946,8 +8082,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7961,12 +8105,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,12 +8130,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8010,7 +8154,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>36.6</v>
+        <v>37.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,62 +8168,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>44.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8099,27 +8239,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,67 +8269,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8222,8 +8362,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -8237,24 +8385,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8262,22 +8410,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8286,7 +8434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>36.2</v>
+        <v>37.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,65 +8448,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>44.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -8375,27 +8519,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8405,101 +8549,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -8513,12 +8665,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8538,12 +8690,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8562,7 +8714,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>36.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,62 +8728,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>49.9</v>
       </c>
       <c r="Q11" t="n">
         <v>21.5</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>77.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8651,27 +8799,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,67 +8829,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8774,8 +8922,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -8789,12 +8945,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8814,12 +8970,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8994,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>36.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,26 +9008,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.3</v>
+        <v>25.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>10.1</v>
+        <v>23.4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8885,7 +9041,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -8927,12 +9083,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,12 +9098,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8957,67 +9113,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9050,8 +9206,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9065,12 +9229,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9254,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9278,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,26 +9292,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>10.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -9161,7 +9325,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -9203,27 +9367,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,67 +9397,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9490,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9341,24 +9513,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9366,22 +9538,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9390,7 +9562,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>33.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,65 +9576,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>45</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -9479,7 +9647,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -9489,17 +9657,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,101 +9677,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9617,24 +9793,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9642,7 +9818,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9652,12 +9828,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9666,7 +9842,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.6</v>
+        <v>33.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9684,13 +9860,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S15" t="n">
         <v>47.9</v>
@@ -9699,7 +9875,7 @@
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9738,7 +9914,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9755,27 +9931,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,101 +9961,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9893,24 +10077,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9918,22 +10102,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10126,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>27.7</v>
+        <v>32.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9960,22 +10144,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>22.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>36.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9989,7 +10173,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -10014,7 +10198,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,12 +10215,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10230,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10245,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.2967</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -10194,7 +10386,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10410,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10242,7 +10434,7 @@
         <v>9.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S17" t="n">
         <v>40.2</v>
@@ -10430,8 +10622,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -10470,7 +10670,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10694,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10518,7 +10718,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -10706,8 +10906,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -10746,7 +10954,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10978,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10794,7 +11002,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S19" t="n">
         <v>88.7</v>
@@ -10982,8 +11190,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Rate Field</t>

--- a/outputs/daily/hr_rankings_2026-10-08.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-08.xlsx
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1651,7 +1651,7 @@
         <v>29.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
@@ -1661,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2468,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2482,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2495,7 +2491,7 @@
         <v>29.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -2505,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -3263,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3293,17 +3285,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3312,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.8</v>
+        <v>37.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3326,26 +3318,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>49.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R11" t="n">
         <v>29.6</v>
       </c>
       <c r="S11" t="n">
-        <v>44.8</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3359,7 +3351,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3380,7 +3372,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3397,12 +3389,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3412,12 +3404,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3427,97 +3419,97 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -3543,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3573,17 +3565,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3592,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.5</v>
+        <v>36.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3606,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>25.8</v>
+        <v>49.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
         <v>29.6</v>
       </c>
       <c r="S12" t="n">
-        <v>95.5</v>
+        <v>44.8</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3681,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3696,12 +3684,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3711,97 +3699,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -3876,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>35.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3890,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3903,7 +3891,7 @@
         <v>29.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -3913,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4111,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Angel Martínez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4141,17 +4125,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4178,22 +4162,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R14" t="n">
         <v>29.6</v>
       </c>
       <c r="S14" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>45</v>
+        <v>36.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4207,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4228,7 +4212,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4245,7 +4229,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -4255,17 +4239,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4275,97 +4259,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -4391,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4426,12 +4410,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4440,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4454,65 +4438,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.4</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R15" t="n">
         <v>29.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>48.7</v>
+        <v>45</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4529,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4559,97 +4539,97 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -4675,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4705,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4724,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.9</v>
+        <v>27.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4738,11 +4718,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>22.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q16" t="n">
         <v>9.6</v>
@@ -4751,49 +4731,45 @@
         <v>29.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
         <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>36.3</v>
+        <v>72.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4813,7 +4789,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -4823,12 +4799,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4843,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4959,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4989,7 +4965,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5008,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>27.3</v>
+        <v>27.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5022,65 +4998,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R17" t="n">
         <v>29.6</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>12</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5097,7 +5069,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -5107,17 +5079,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5127,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5243,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5273,7 +5245,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5292,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5306,11 +5278,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
         <v>9.699999999999999</v>
@@ -5319,52 +5291,48 @@
         <v>29.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5381,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5396,7 +5364,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5411,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5527,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5557,7 +5525,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5576,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5590,11 +5558,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
         <v>9.699999999999999</v>
@@ -5603,49 +5571,45 @@
         <v>29.6</v>
       </c>
       <c r="S19" t="n">
-        <v>88.7</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>43.1</v>
+        <v>28.9</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5665,27 +5629,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5695,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -7026,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7040,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7053,7 +7017,7 @@
         <v>29.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
@@ -7063,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7870,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7884,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7897,7 +7857,7 @@
         <v>29.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -7907,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -8665,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8695,17 +8651,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -8714,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.8</v>
+        <v>37.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8728,26 +8684,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>49.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R11" t="n">
         <v>29.6</v>
       </c>
       <c r="S11" t="n">
-        <v>44.8</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8761,7 +8717,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -8782,7 +8738,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8799,12 +8755,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -8814,12 +8770,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8829,97 +8785,97 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -8945,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8975,17 +8931,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8994,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.5</v>
+        <v>36.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9008,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>25.8</v>
+        <v>49.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
         <v>29.6</v>
       </c>
       <c r="S12" t="n">
-        <v>95.5</v>
+        <v>44.8</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -9083,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -9098,12 +9050,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9113,97 +9065,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -9278,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>35.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9292,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9305,7 +9257,7 @@
         <v>29.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -9315,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9513,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Angel Martínez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9543,17 +9491,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9580,22 +9528,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R14" t="n">
         <v>29.6</v>
       </c>
       <c r="S14" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>45</v>
+        <v>36.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9609,7 +9557,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9630,7 +9578,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -9647,7 +9595,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -9657,17 +9605,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9677,97 +9625,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -9793,24 +9741,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9828,12 +9776,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9842,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9856,65 +9804,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.4</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R15" t="n">
         <v>29.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>48.7</v>
+        <v>45</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9931,27 +9875,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9961,97 +9905,97 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -10077,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10107,7 +10051,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10126,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.9</v>
+        <v>27.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10140,11 +10084,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>22.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q16" t="n">
         <v>9.6</v>
@@ -10153,49 +10097,45 @@
         <v>29.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
         <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>36.3</v>
+        <v>72.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10215,7 +10155,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -10225,12 +10165,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -10245,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10361,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10391,7 +10331,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10410,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>27.3</v>
+        <v>27.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10424,65 +10364,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R17" t="n">
         <v>29.6</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>12</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10499,7 +10435,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -10509,17 +10445,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10529,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10645,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10675,7 +10611,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10694,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10708,11 +10644,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
         <v>9.699999999999999</v>
@@ -10721,52 +10657,48 @@
         <v>29.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10783,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10798,7 +10730,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -10813,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10929,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10959,7 +10891,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10978,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10992,11 +10924,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
         <v>9.699999999999999</v>
@@ -11005,49 +10937,45 @@
         <v>29.6</v>
       </c>
       <c r="S19" t="n">
-        <v>88.7</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>43.1</v>
+        <v>28.9</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11067,27 +10995,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -11097,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
